--- a/gas_data.xlsx
+++ b/gas_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calebskinner/Desktop/Rock Chucks/Miscellaneous/Truly Miscellaneous/Miscellaneous/Gas Mileage/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calebskinner/Desktop/Rock Chucks/Miscellaneous/Truly Miscellaneous/Miscellaneous/GasMileage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F8E0B5-6469-8045-8FF4-BD81993B10C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4DBAF6-4021-1647-81B8-B3E22278A030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11200" yWindow="800" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
   </bookViews>

--- a/gas_data.xlsx
+++ b/gas_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calebskinner/Desktop/Rock Chucks/Miscellaneous/Truly Miscellaneous/Miscellaneous/GasMileage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4DBAF6-4021-1647-81B8-B3E22278A030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02894BC-D068-8649-8959-8722967A5233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="800" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
+    <workbookView xWindow="11200" yWindow="720" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,18 +134,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,7 +157,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1932,7 +1926,7 @@
         <v>6</v>
       </c>
       <c r="C103" s="1">
-        <v>469</v>
+        <v>500</v>
       </c>
       <c r="D103">
         <v>12.5</v>
@@ -1946,7 +1940,7 @@
         <v>4</v>
       </c>
       <c r="C104" s="2">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="D104">
         <v>9</v>
@@ -1960,7 +1954,7 @@
         <v>10</v>
       </c>
       <c r="C105" s="1">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D105">
         <v>5.4</v>

--- a/gas_data.xlsx
+++ b/gas_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calebskinner/Desktop/Rock Chucks/Miscellaneous/Truly Miscellaneous/Miscellaneous/GasMileage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02894BC-D068-8649-8959-8722967A5233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3099434A-2D67-6045-8F0C-F9D61D8AFF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="720" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
+    <workbookView xWindow="-2060" yWindow="660" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -154,10 +154,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1939,7 +1938,7 @@
       <c r="B104" t="s">
         <v>4</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="1">
         <v>335</v>
       </c>
       <c r="D104">

--- a/gas_data.xlsx
+++ b/gas_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calebskinner/Desktop/Rock Chucks/Miscellaneous/Truly Miscellaneous/Miscellaneous/GasMileage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3099434A-2D67-6045-8F0C-F9D61D8AFF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5187F9-2E25-7548-9048-1E1BCE5DFEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2060" yWindow="660" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
+    <workbookView xWindow="11200" yWindow="700" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="27">
   <si>
     <t>CRV</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>eExpress</t>
+  </si>
+  <si>
+    <t>Rogue</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89D0EF3-4547-5446-A057-08125E114860}">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1495,21 +1498,21 @@
       <c r="B72" t="s">
         <v>5</v>
       </c>
-      <c r="C72" s="1"/>
+      <c r="C72" s="1">
+        <v>227</v>
+      </c>
+      <c r="D72">
+        <v>9.8620000000000001</v>
+      </c>
     </row>
     <row r="73" spans="1:4" ht="17">
-      <c r="A73" s="1" t="s">
-        <v>1</v>
+      <c r="A73" t="s">
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="1">
-        <v>361</v>
-      </c>
-      <c r="D73">
-        <v>10.3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C73" s="1"/>
     </row>
     <row r="74" spans="1:4" ht="17">
       <c r="A74" s="1" t="s">
@@ -1519,10 +1522,10 @@
         <v>7</v>
       </c>
       <c r="C74" s="1">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D74">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="17">
@@ -1530,13 +1533,13 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C75" s="1">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="D75">
-        <v>10.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="17">
@@ -1544,13 +1547,13 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C76" s="1">
-        <v>94</v>
+        <v>382</v>
       </c>
       <c r="D76">
-        <v>2.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="17">
@@ -1558,13 +1561,13 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C77" s="1">
-        <v>453</v>
+        <v>94</v>
       </c>
       <c r="D77">
-        <v>11.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="17">
@@ -1572,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C78" s="1">
-        <v>372</v>
+        <v>453</v>
       </c>
       <c r="D78">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17">
@@ -1589,10 +1592,10 @@
         <v>10</v>
       </c>
       <c r="C79" s="1">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="D79">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="17">
@@ -1600,13 +1603,13 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C80" s="1">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="D80">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="17">
@@ -1614,13 +1617,13 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C81" s="1">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="D81">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="17">
@@ -1628,13 +1631,13 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C82" s="1">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="D82">
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="17">
@@ -1642,13 +1645,13 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C83" s="1">
-        <v>437</v>
+        <v>275</v>
       </c>
       <c r="D83">
-        <v>11</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17">
@@ -1656,13 +1659,13 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C84" s="1">
-        <v>334</v>
+        <v>437</v>
       </c>
       <c r="D84">
-        <v>11.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="17">
@@ -1670,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C85" s="1">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="D85">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="17">
@@ -1684,10 +1687,10 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C86" s="1">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="D86">
         <v>11.4</v>
@@ -1698,10 +1701,10 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C87" s="1">
-        <v>396</v>
+        <v>272</v>
       </c>
       <c r="D87">
         <v>11.4</v>
@@ -1712,13 +1715,13 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C88" s="1">
         <v>396</v>
       </c>
       <c r="D88">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="17">
@@ -1726,13 +1729,13 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C89" s="1">
-        <v>260</v>
+        <v>396</v>
       </c>
       <c r="D89">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="17">
@@ -1740,10 +1743,10 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C90" s="1">
-        <v>332</v>
+        <v>260</v>
       </c>
       <c r="D90">
         <v>11.2</v>
@@ -1757,10 +1760,10 @@
         <v>9</v>
       </c>
       <c r="C91" s="1">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D91">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="17">
@@ -1771,10 +1774,10 @@
         <v>9</v>
       </c>
       <c r="C92" s="1">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="D92">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="17">
@@ -1782,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C93" s="1">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="D93">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="17">
@@ -1799,10 +1802,10 @@
         <v>6</v>
       </c>
       <c r="C94" s="1">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="D94">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="17">
@@ -1810,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C95" s="1">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D95">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="17">
@@ -1824,13 +1827,13 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C96" s="1">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="D96">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="17">
@@ -1838,13 +1841,13 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C97" s="1">
-        <v>421</v>
+        <v>336</v>
       </c>
       <c r="D97">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="17">
@@ -1852,13 +1855,13 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C98" s="1">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="D98">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17">
@@ -1866,13 +1869,13 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C99" s="1">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="D99">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="17">
@@ -1883,10 +1886,10 @@
         <v>9</v>
       </c>
       <c r="C100" s="1">
-        <v>289</v>
+        <v>428</v>
       </c>
       <c r="D100">
-        <v>12</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="17">
@@ -1897,10 +1900,10 @@
         <v>9</v>
       </c>
       <c r="C101" s="1">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D101">
-        <v>9.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17">
@@ -1908,13 +1911,13 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D102">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="17">
@@ -1922,13 +1925,13 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C103" s="1">
-        <v>500</v>
+        <v>282</v>
       </c>
       <c r="D103">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="17">
@@ -1936,13 +1939,13 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C104" s="1">
-        <v>335</v>
+        <v>500</v>
       </c>
       <c r="D104">
-        <v>9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="17">
@@ -1950,13 +1953,13 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C105" s="1">
-        <v>194</v>
+        <v>335</v>
       </c>
       <c r="D105">
-        <v>5.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="17">
@@ -1964,13 +1967,13 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C106" s="1">
-        <v>359</v>
+        <v>194</v>
       </c>
       <c r="D106">
-        <v>11.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="17">
@@ -1978,13 +1981,13 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C107" s="1">
-        <v>276</v>
+        <v>359</v>
       </c>
       <c r="D107">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="17">
@@ -1995,10 +1998,10 @@
         <v>9</v>
       </c>
       <c r="C108" s="1">
-        <v>391</v>
+        <v>276</v>
       </c>
       <c r="D108">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="17">
@@ -2009,10 +2012,10 @@
         <v>9</v>
       </c>
       <c r="C109" s="1">
-        <v>247</v>
+        <v>391</v>
       </c>
       <c r="D109">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="17">
@@ -2023,10 +2026,10 @@
         <v>9</v>
       </c>
       <c r="C110" s="1">
-        <v>317</v>
+        <v>247</v>
       </c>
       <c r="D110">
-        <v>10.199999999999999</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="17">
@@ -2034,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C111" s="1">
-        <v>388</v>
+        <v>317</v>
       </c>
       <c r="D111">
-        <v>11.3</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="17">
@@ -2048,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C112" s="1">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="D112">
-        <v>10.199999999999999</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="17">
@@ -2062,13 +2065,13 @@
         <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C113" s="1">
-        <v>410</v>
+        <v>335</v>
       </c>
       <c r="D113">
-        <v>11.2</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17">
@@ -2076,13 +2079,13 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C114" s="1">
-        <v>279</v>
+        <v>410</v>
       </c>
       <c r="D114">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="17">
@@ -2090,7 +2093,57 @@
         <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="C115" s="1">
+        <v>279</v>
+      </c>
+      <c r="D115">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="17">
+      <c r="A116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="1">
+        <v>233</v>
+      </c>
+      <c r="D116">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="17">
+      <c r="A117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="17">
+      <c r="A118" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D118">
+        <v>10.879</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="17">
+      <c r="A119" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/gas_data.xlsx
+++ b/gas_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calebskinner/Desktop/Rock Chucks/Miscellaneous/Truly Miscellaneous/Miscellaneous/GasMileage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5187F9-2E25-7548-9048-1E1BCE5DFEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3858204-47F2-5844-BE00-056D80B18925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11200" yWindow="700" windowWidth="19040" windowHeight="17340" xr2:uid="{CB6065DC-DFC6-1445-B6D3-B4648FEC9455}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="27">
   <si>
     <t>CRV</t>
   </si>
@@ -494,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89D0EF3-4547-5446-A057-08125E114860}">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2123,26 +2123,55 @@
       <c r="B117" t="s">
         <v>9</v>
       </c>
+      <c r="C117" s="1">
+        <v>331</v>
+      </c>
+      <c r="D117">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="118" spans="1:4" ht="17">
       <c r="A118" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D118">
-        <v>10.879</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="1"/>
     </row>
     <row r="119" spans="1:4" ht="17">
       <c r="A119" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D119">
+        <v>10.879</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="17">
+      <c r="A120" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4</v>
+      </c>
+      <c r="C120" s="1">
+        <v>290</v>
+      </c>
+      <c r="D120">
+        <v>13.663</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="17">
+      <c r="A121" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B121" t="s">
         <v>4</v>
       </c>
     </row>
